--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Hiopos Lleida.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Hiopos Lleida.xlsx
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>31.8595</v>
+        <v>26.9946</v>
       </c>
       <c r="E2" t="n">
-        <v>31.7564</v>
+        <v>32.7956</v>
       </c>
       <c r="F2" t="n">
-        <v>0.103699999999999</v>
+        <v>-5.8009</v>
       </c>
       <c r="G2" t="n">
-        <v>16.2797</v>
+        <v>11.1063</v>
       </c>
       <c r="H2" t="n">
-        <v>10.1346</v>
+        <v>9.896800000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>6.145</v>
+        <v>1.2099</v>
       </c>
       <c r="J2" t="n">
-        <v>27.1801</v>
+        <v>27.2633</v>
       </c>
       <c r="K2" t="n">
-        <v>20.669</v>
+        <v>22.2307</v>
       </c>
       <c r="L2" t="n">
-        <v>6.511799999999999</v>
+        <v>5.0323</v>
       </c>
       <c r="M2" t="n">
-        <v>-10.9002</v>
+        <v>-16.1568</v>
       </c>
       <c r="N2" t="n">
-        <v>-10.5339</v>
+        <v>-12.3339</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3664000000000002</v>
+        <v>-3.8224</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.134</v>
+        <v>-0.2274999999999996</v>
       </c>
       <c r="Q2" t="n">
-        <v>-26.5396</v>
+        <v>-27.7713</v>
       </c>
       <c r="R2" t="n">
-        <v>25.4055</v>
+        <v>27.5437</v>
       </c>
       <c r="S2" t="n">
-        <v>13.468</v>
+        <v>11.6484</v>
       </c>
       <c r="T2" t="n">
-        <v>9.872199999999999</v>
+        <v>8.201000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>3.596200000000001</v>
+        <v>3.4473</v>
       </c>
       <c r="V2" t="n">
-        <v>3.2462</v>
+        <v>4.4674</v>
       </c>
       <c r="W2" t="n">
-        <v>21.2433</v>
+        <v>25.1025</v>
       </c>
       <c r="X2" t="n">
-        <v>-17.9975</v>
+        <v>-20.6352</v>
       </c>
     </row>
     <row r="3">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>15.3323</v>
+        <v>11.8318</v>
       </c>
       <c r="E3" t="n">
-        <v>8.626300000000001</v>
+        <v>4.837200000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>6.706</v>
+        <v>6.994800000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-6.356199999999999</v>
+        <v>-9.767299999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.979699999999998</v>
+        <v>-7.8194</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.3767</v>
+        <v>-1.9477</v>
       </c>
       <c r="J3" t="n">
-        <v>17.2483</v>
+        <v>17.5671</v>
       </c>
       <c r="K3" t="n">
-        <v>8.560499999999999</v>
+        <v>7.7036</v>
       </c>
       <c r="L3" t="n">
-        <v>8.687900000000001</v>
+        <v>9.863199999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-23.6047</v>
+        <v>-27.3342</v>
       </c>
       <c r="N3" t="n">
-        <v>-12.5404</v>
+        <v>-15.5234</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.0642</v>
+        <v>-11.811</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.2683</v>
+        <v>-3.186800000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-48.5425</v>
+        <v>-59.1845</v>
       </c>
       <c r="R3" t="n">
-        <v>46.2739</v>
+        <v>55.9976</v>
       </c>
       <c r="S3" t="n">
-        <v>14.4381</v>
+        <v>15.2051</v>
       </c>
       <c r="T3" t="n">
-        <v>4.3437</v>
+        <v>5.4114</v>
       </c>
       <c r="U3" t="n">
-        <v>10.0942</v>
+        <v>9.793900000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>9.518799999999999</v>
+        <v>9.580699999999998</v>
       </c>
       <c r="W3" t="n">
-        <v>35.5763</v>
+        <v>41.0427</v>
       </c>
       <c r="X3" t="n">
-        <v>-26.0579</v>
+        <v>-31.462</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>13.3398</v>
+        <v>10.33</v>
       </c>
       <c r="E4" t="n">
-        <v>22.5652</v>
+        <v>39.0536</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.2257</v>
+        <v>-28.7238</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.1417</v>
+        <v>22.4576</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.9812</v>
+        <v>23.6095</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1605</v>
+        <v>-1.1519</v>
       </c>
       <c r="J4" t="n">
-        <v>18.459</v>
+        <v>38.7481</v>
       </c>
       <c r="K4" t="n">
-        <v>7.5132</v>
+        <v>32.0829</v>
       </c>
       <c r="L4" t="n">
-        <v>10.946</v>
+        <v>6.6651</v>
       </c>
       <c r="M4" t="n">
-        <v>-24.6008</v>
+        <v>-16.2907</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.4946</v>
+        <v>-8.4735</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.1067</v>
+        <v>-7.8176</v>
       </c>
       <c r="P4" t="n">
-        <v>-9.073499999999999</v>
+        <v>-10.9264</v>
       </c>
       <c r="Q4" t="n">
-        <v>-56.4814</v>
+        <v>-39.1527</v>
       </c>
       <c r="R4" t="n">
-        <v>47.4081</v>
+        <v>28.2268</v>
       </c>
       <c r="S4" t="n">
-        <v>-18.8484</v>
+        <v>27.8126</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.6941</v>
+        <v>25.6378</v>
       </c>
       <c r="U4" t="n">
-        <v>-8.154400000000001</v>
+        <v>2.175</v>
       </c>
       <c r="V4" t="n">
-        <v>47.4025</v>
+        <v>-29.0136</v>
       </c>
       <c r="W4" t="n">
-        <v>71.2813</v>
+        <v>13.8208</v>
       </c>
       <c r="X4" t="n">
-        <v>-23.8788</v>
+        <v>-42.8348</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>2.078099999999999</v>
+        <v>5.718299999999997</v>
       </c>
       <c r="E5" t="n">
-        <v>26.417</v>
+        <v>24.0415</v>
       </c>
       <c r="F5" t="n">
-        <v>-24.3388</v>
+        <v>-18.3235</v>
       </c>
       <c r="G5" t="n">
-        <v>15.007</v>
+        <v>-15.4229</v>
       </c>
       <c r="H5" t="n">
-        <v>17.1111</v>
+        <v>-6.831399999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.104499999999999</v>
+        <v>-8.591799999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>27.8725</v>
+        <v>21.0836</v>
       </c>
       <c r="K5" t="n">
-        <v>22.9096</v>
+        <v>9.2666</v>
       </c>
       <c r="L5" t="n">
-        <v>4.9634</v>
+        <v>11.8171</v>
       </c>
       <c r="M5" t="n">
-        <v>-12.8658</v>
+        <v>-36.5073</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.7983</v>
+        <v>-16.0982</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.0673</v>
+        <v>-20.4088</v>
       </c>
       <c r="P5" t="n">
-        <v>-10.4344</v>
+        <v>-12.7476</v>
       </c>
       <c r="Q5" t="n">
-        <v>-32.2103</v>
+        <v>-68.2894</v>
       </c>
       <c r="R5" t="n">
-        <v>21.7762</v>
+        <v>55.5423</v>
       </c>
       <c r="S5" t="n">
-        <v>20.0664</v>
+        <v>-20.5217</v>
       </c>
       <c r="T5" t="n">
-        <v>18.7669</v>
+        <v>-10.8234</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2994</v>
+        <v>-9.6981</v>
       </c>
       <c r="V5" t="n">
-        <v>-22.5604</v>
+        <v>54.4106</v>
       </c>
       <c r="W5" t="n">
-        <v>11.9876</v>
+        <v>82.07089999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-34.548</v>
+        <v>-27.6601</v>
       </c>
     </row>
     <row r="6">
@@ -877,37 +877,37 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6907</v>
+        <v>-1.697</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3652</v>
+        <v>-1.3732</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3255</v>
+        <v>-0.3238</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4847</v>
+        <v>-1.4903</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4847</v>
+        <v>-1.4903</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2956</v>
+        <v>-1.3035</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2956</v>
+        <v>-1.3035</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.206</v>
+        <v>-0.2067</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1364</v>
+        <v>-0.137</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,22 +955,22 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1232</v>
+        <v>-2.125</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2037</v>
+        <v>-1.2079</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9195</v>
+        <v>-0.9171</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7622</v>
+        <v>-0.7592</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -982,31 +982,31 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7622</v>
+        <v>-0.7592</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.767799999999998</v>
+        <v>-3.282299999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.972499999999998</v>
+        <v>-5.0208</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7951999999999997</v>
+        <v>1.7383</v>
       </c>
       <c r="G8" t="n">
-        <v>2.432699999999998</v>
+        <v>5.675200000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>7.728899999999999</v>
+        <v>12.3437</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.2961</v>
+        <v>-6.6685</v>
       </c>
       <c r="J8" t="n">
-        <v>32.834</v>
+        <v>45.3425</v>
       </c>
       <c r="K8" t="n">
-        <v>21.9495</v>
+        <v>31.1978</v>
       </c>
       <c r="L8" t="n">
-        <v>10.884</v>
+        <v>14.1443</v>
       </c>
       <c r="M8" t="n">
-        <v>-30.4006</v>
+        <v>-39.6672</v>
       </c>
       <c r="N8" t="n">
-        <v>-14.221</v>
+        <v>-18.8544</v>
       </c>
       <c r="O8" t="n">
-        <v>-16.1798</v>
+        <v>-20.8128</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.846400000000001</v>
+        <v>-11.6091</v>
       </c>
       <c r="Q8" t="n">
-        <v>-51.7179</v>
+        <v>-66.9237</v>
       </c>
       <c r="R8" t="n">
-        <v>42.8717</v>
+        <v>55.3148</v>
       </c>
       <c r="S8" t="n">
-        <v>-6.137</v>
+        <v>-9.754999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-10.6303</v>
+        <v>-15.8672</v>
       </c>
       <c r="U8" t="n">
-        <v>4.4935</v>
+        <v>6.1124</v>
       </c>
       <c r="V8" t="n">
-        <v>9.782699999999998</v>
+        <v>12.4067</v>
       </c>
       <c r="W8" t="n">
-        <v>27.5422</v>
+        <v>32.4283</v>
       </c>
       <c r="X8" t="n">
-        <v>-17.7596</v>
+        <v>-20.0213</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>I. DABO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.575200000000001</v>
+        <v>-4.6955</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.552099999999998</v>
+        <v>-0.6471</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.023099999999999</v>
+        <v>-4.0485</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4165000000000001</v>
+        <v>-0.6957</v>
       </c>
       <c r="H9" t="n">
-        <v>7.232</v>
+        <v>-0.4337</v>
       </c>
       <c r="I9" t="n">
-        <v>-6.8154</v>
+        <v>-0.2619</v>
       </c>
       <c r="J9" t="n">
-        <v>15.0277</v>
+        <v>0.9093</v>
       </c>
       <c r="K9" t="n">
-        <v>13.366</v>
+        <v>0.3135</v>
       </c>
       <c r="L9" t="n">
-        <v>1.6621</v>
+        <v>0.5958</v>
       </c>
       <c r="M9" t="n">
-        <v>-14.6112</v>
+        <v>-1.605</v>
       </c>
       <c r="N9" t="n">
-        <v>-6.133999999999999</v>
+        <v>-0.7472</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.477399999999999</v>
+        <v>-0.8577</v>
       </c>
       <c r="P9" t="n">
-        <v>11.3415</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-16.5589</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>27.9003</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.0337</v>
+        <v>-0.6827</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.242699999999999</v>
+        <v>-0.4182</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.7909</v>
+        <v>-0.2645</v>
       </c>
       <c r="V9" t="n">
-        <v>-11.2999</v>
+        <v>-2.1789</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2216</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.5213</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="10">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.207100000000001</v>
+        <v>-5.4288</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3814999999999993</v>
+        <v>1.773099999999998</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.5881</v>
+        <v>-7.201699999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-15.8282</v>
+        <v>-14.7188</v>
       </c>
       <c r="H10" t="n">
-        <v>-10.1631</v>
+        <v>-3.005299999999998</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.6655</v>
+        <v>-11.7135</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8711</v>
+        <v>13.5492</v>
       </c>
       <c r="K10" t="n">
-        <v>-6.5027</v>
+        <v>1.894</v>
       </c>
       <c r="L10" t="n">
-        <v>10.374</v>
+        <v>11.6549</v>
       </c>
       <c r="M10" t="n">
-        <v>-19.6997</v>
+        <v>-28.2682</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.6602</v>
+        <v>-4.899500000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-16.0392</v>
+        <v>-23.3682</v>
       </c>
       <c r="P10" t="n">
-        <v>3.1757</v>
+        <v>0.2278000000000004</v>
       </c>
       <c r="Q10" t="n">
-        <v>-21.7761</v>
+        <v>-32.324</v>
       </c>
       <c r="R10" t="n">
-        <v>24.952</v>
+        <v>32.5519</v>
       </c>
       <c r="S10" t="n">
-        <v>8.1883</v>
+        <v>9.047499999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>7.616</v>
+        <v>7.831</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5727000000000001</v>
+        <v>1.2167</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2574000000000005</v>
+        <v>0.01510000000000006</v>
       </c>
       <c r="W10" t="n">
-        <v>10.6699</v>
+        <v>12.7165</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.4125</v>
+        <v>-12.7013</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. DABO</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6996</v>
+        <v>-12.3123</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6325</v>
+        <v>0.6137999999999986</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.0671</v>
+        <v>-12.9259</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7009000000000001</v>
+        <v>-4.305</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4343</v>
+        <v>12.7266</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2665</v>
+        <v>-17.0312</v>
       </c>
       <c r="J11" t="n">
-        <v>0.919</v>
+        <v>21.1299</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3219</v>
+        <v>21.1016</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5971</v>
+        <v>0.02820000000000034</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6198</v>
+        <v>-25.435</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7563</v>
+        <v>-8.375200000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8636</v>
+        <v>-17.0602</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>14.5684</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-18.8934</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>33.4619</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6793</v>
+        <v>-7.678</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4174</v>
+        <v>-3.5158</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2619</v>
+        <v>-4.162</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1853</v>
+        <v>-14.8977</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.8934</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-16.791</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.260199999999999</v>
+        <v>-15.4856</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3635</v>
+        <v>-5.6547</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.8968</v>
+        <v>-9.830500000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.879</v>
+        <v>-26.4352</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.404</v>
+        <v>-12.2007</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5250999999999999</v>
+        <v>-14.2341</v>
       </c>
       <c r="J12" t="n">
-        <v>3.0342</v>
+        <v>8.594999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5097</v>
+        <v>4.5046</v>
       </c>
       <c r="L12" t="n">
-        <v>1.5246</v>
+        <v>4.0906</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.9131</v>
+        <v>-35.0303</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.9137</v>
+        <v>-16.7056</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9994000000000001</v>
+        <v>-18.3249</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>21.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2684</v>
+        <v>-13.2027</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>34.3726</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4248</v>
+        <v>-4.116</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7723</v>
+        <v>-8.1432</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3475</v>
+        <v>4.0279</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.9566</v>
+        <v>-6.1039</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6428999999999999</v>
+        <v>7.096699999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.5994</v>
+        <v>-13.2006</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>A. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,70 +1420,70 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.4245</v>
+        <v>-17.8092</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.624000000000001</v>
+        <v>-5.3896</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.8008</v>
+        <v>-12.4195</v>
       </c>
       <c r="G13" t="n">
-        <v>-21.6164</v>
+        <v>-11.0999</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.2284</v>
+        <v>-7.7241</v>
       </c>
       <c r="I13" t="n">
-        <v>-10.3875</v>
+        <v>-3.3758</v>
       </c>
       <c r="J13" t="n">
-        <v>7.305899999999999</v>
+        <v>3.025</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4297</v>
+        <v>-0.1236999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>2.8766</v>
+        <v>3.1487</v>
       </c>
       <c r="M13" t="n">
-        <v>-28.9225</v>
+        <v>-14.125</v>
       </c>
       <c r="N13" t="n">
-        <v>-15.6582</v>
+        <v>-7.6006</v>
       </c>
       <c r="O13" t="n">
-        <v>-13.2643</v>
+        <v>-6.5245</v>
       </c>
       <c r="P13" t="n">
-        <v>18.3735</v>
+        <v>-1.8212</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.0221</v>
+        <v>-9.3331</v>
       </c>
       <c r="R13" t="n">
-        <v>30.3958</v>
+        <v>7.5119</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.5343</v>
+        <v>1.5622</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.7213</v>
+        <v>0.9032</v>
       </c>
       <c r="U13" t="n">
-        <v>5.1866</v>
+        <v>0.659</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.6472</v>
+        <v>-6.4504</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8133</v>
+        <v>0.0149999999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.4606</v>
+        <v>-6.4653</v>
       </c>
     </row>
     <row r="14">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.4478</v>
+        <v>-24.2967</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6942</v>
+        <v>-13.026</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.7536</v>
+        <v>-11.2706</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4392</v>
+        <v>6.1402</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2289</v>
+        <v>5.8229</v>
       </c>
       <c r="I14" t="n">
-        <v>1.21</v>
+        <v>0.3171999999999992</v>
       </c>
       <c r="J14" t="n">
-        <v>13.871</v>
+        <v>19.6519</v>
       </c>
       <c r="K14" t="n">
-        <v>8.7646</v>
+        <v>11.5771</v>
       </c>
       <c r="L14" t="n">
-        <v>5.106400000000001</v>
+        <v>8.0749</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.431799999999999</v>
+        <v>-13.5118</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.5355</v>
+        <v>-5.7542</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.8963</v>
+        <v>-7.7577</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.444100000000001</v>
+        <v>-11.6094</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.7857</v>
+        <v>-30.5026</v>
       </c>
       <c r="R14" t="n">
-        <v>11.3416</v>
+        <v>18.8933</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2836</v>
+        <v>-4.806999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.604</v>
+        <v>-6.777</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3204</v>
+        <v>1.9703</v>
       </c>
       <c r="V14" t="n">
-        <v>-9.1592</v>
+        <v>-14.0204</v>
       </c>
       <c r="W14" t="n">
-        <v>3.8244</v>
+        <v>4.6021</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.9836</v>
+        <v>-18.6224</v>
       </c>
     </row>
     <row r="15">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.1891</v>
+        <v>-27.5737</v>
       </c>
       <c r="E15" t="n">
-        <v>-28.4146</v>
+        <v>-29.7031</v>
       </c>
       <c r="F15" t="n">
-        <v>9.2256</v>
+        <v>2.129300000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.889499999999999</v>
+        <v>-9.418799999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6021</v>
+        <v>7.3565</v>
       </c>
       <c r="I15" t="n">
-        <v>-10.4916</v>
+        <v>-16.7755</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1074</v>
+        <v>4.870099999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>7.024299999999999</v>
+        <v>12.0232</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.916700000000001</v>
+        <v>-7.152800000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-8.996600000000001</v>
+        <v>-14.2894</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.4219</v>
+        <v>-4.666700000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.575</v>
+        <v>-9.6227</v>
       </c>
       <c r="P15" t="n">
-        <v>-9.754100000000001</v>
+        <v>-11.3818</v>
       </c>
       <c r="Q15" t="n">
-        <v>-33.1178</v>
+        <v>-38.9253</v>
       </c>
       <c r="R15" t="n">
-        <v>23.3639</v>
+        <v>27.5436</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7841000000000002</v>
+        <v>2.3702</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2612</v>
+        <v>-0.3370000000000004</v>
       </c>
       <c r="U15" t="n">
-        <v>2.0448</v>
+        <v>2.707</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.3295</v>
+        <v>-9.1433</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8567</v>
+        <v>4.688499999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.1863</v>
+        <v>-13.8317</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>-27.5571</v>
+        <v>-27.5971</v>
       </c>
       <c r="E16" t="n">
-        <v>-18.8693</v>
+        <v>-19.18</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.687799999999999</v>
+        <v>-8.417199999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.0583</v>
+        <v>-7.035200000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4850000000000005</v>
+        <v>-0.4663999999999998</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.5732</v>
+        <v>-6.5692</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4642000000000007</v>
+        <v>-0.6634000000000005</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5657999999999999</v>
+        <v>0.4732999999999998</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.0298</v>
+        <v>-1.1367</v>
       </c>
       <c r="M16" t="n">
-        <v>-6.5942</v>
+        <v>-6.371799999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0509</v>
+        <v>-0.9394000000000002</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.5434</v>
+        <v>-5.432</v>
       </c>
       <c r="P16" t="n">
-        <v>-6.1246</v>
+        <v>-6.1462</v>
       </c>
       <c r="Q16" t="n">
-        <v>-17.9197</v>
+        <v>-17.9829</v>
       </c>
       <c r="R16" t="n">
-        <v>11.7953</v>
+        <v>11.8369</v>
       </c>
       <c r="S16" t="n">
-        <v>-10.9939</v>
+        <v>-11.0331</v>
       </c>
       <c r="T16" t="n">
-        <v>-6.3029</v>
+        <v>-6.3111</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.6911</v>
+        <v>-4.7217</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.3807</v>
+        <v>-3.3826</v>
       </c>
       <c r="W16" t="n">
-        <v>5.8172</v>
+        <v>5.7779</v>
       </c>
       <c r="X16" t="n">
-        <v>-9.198</v>
+        <v>-9.160500000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>-48.7092</v>
+        <v>-59.6153</v>
       </c>
       <c r="E17" t="n">
-        <v>-37.6719</v>
+        <v>-47.10429999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.0371</v>
+        <v>-12.5106</v>
       </c>
       <c r="G17" t="n">
-        <v>-13.5991</v>
+        <v>-21.0415</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8178999999999994</v>
+        <v>-2.4238</v>
       </c>
       <c r="I17" t="n">
-        <v>-12.7809</v>
+        <v>-18.617</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1707</v>
+        <v>-2.4369</v>
       </c>
       <c r="K17" t="n">
-        <v>9.0175</v>
+        <v>8.7095</v>
       </c>
       <c r="L17" t="n">
-        <v>-6.8469</v>
+        <v>-11.1462</v>
       </c>
       <c r="M17" t="n">
-        <v>-15.7695</v>
+        <v>-18.6052</v>
       </c>
       <c r="N17" t="n">
-        <v>-9.835599999999999</v>
+        <v>-11.1336</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.934</v>
+        <v>-7.4712</v>
       </c>
       <c r="P17" t="n">
-        <v>-8.392900000000001</v>
+        <v>-8.877700000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-41.2835</v>
+        <v>-44.8437</v>
       </c>
       <c r="R17" t="n">
-        <v>32.8909</v>
+        <v>35.9661</v>
       </c>
       <c r="S17" t="n">
-        <v>-10.1468</v>
+        <v>-12.4931</v>
       </c>
       <c r="T17" t="n">
-        <v>-10.9966</v>
+        <v>-12.9129</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8493000000000003</v>
+        <v>0.4202000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-16.5704</v>
+        <v>-17.2029</v>
       </c>
       <c r="W17" t="n">
-        <v>12.4374</v>
+        <v>13.0887</v>
       </c>
       <c r="X17" t="n">
-        <v>-29.0077</v>
+        <v>-30.2915</v>
       </c>
     </row>
     <row r="18">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>-77.26139999999999</v>
+        <v>-78.40349999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-59.6439</v>
+        <v>-62.2215</v>
       </c>
       <c r="F18" t="n">
-        <v>-17.6177</v>
+        <v>-16.182</v>
       </c>
       <c r="G18" t="n">
-        <v>-39.8003</v>
+        <v>-44.8432</v>
       </c>
       <c r="H18" t="n">
-        <v>-23.287</v>
+        <v>-25.7257</v>
       </c>
       <c r="I18" t="n">
-        <v>-16.5132</v>
+        <v>-19.1174</v>
       </c>
       <c r="J18" t="n">
-        <v>-14.2359</v>
+        <v>-17.0262</v>
       </c>
       <c r="K18" t="n">
-        <v>-14.6017</v>
+        <v>-16.2003</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3652999999999993</v>
+        <v>-0.8258000000000002</v>
       </c>
       <c r="M18" t="n">
-        <v>-25.564</v>
+        <v>-27.8173</v>
       </c>
       <c r="N18" t="n">
-        <v>-8.6852</v>
+        <v>-9.525399999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-16.8784</v>
+        <v>-18.2919</v>
       </c>
       <c r="P18" t="n">
-        <v>-25.8591</v>
+        <v>-20.0316</v>
       </c>
       <c r="Q18" t="n">
-        <v>-59.4306</v>
+        <v>-60.7779</v>
       </c>
       <c r="R18" t="n">
-        <v>33.5712</v>
+        <v>40.7462</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3545999999999998</v>
+        <v>0.7376000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6653999999999999</v>
+        <v>0.6721000000000004</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3105000000000002</v>
+        <v>0.06560000000000021</v>
       </c>
       <c r="V18" t="n">
-        <v>-11.2482</v>
+        <v>-14.2663</v>
       </c>
       <c r="W18" t="n">
-        <v>14.6873</v>
+        <v>14.9102</v>
       </c>
       <c r="X18" t="n">
-        <v>-25.9352</v>
+        <v>-29.1767</v>
       </c>
     </row>
     <row r="19">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>-156.3032</v>
+        <v>-225.4473</v>
       </c>
       <c r="E19" t="n">
-        <v>-69.26100000000001</v>
+        <v>-87.41340000000002</v>
       </c>
       <c r="F19" t="n">
-        <v>-87.0415</v>
+        <v>-138.0332</v>
       </c>
       <c r="G19" t="n">
-        <v>-82.54140000000001</v>
+        <v>-121.6537</v>
       </c>
       <c r="H19" t="n">
-        <v>-9.243599999999997</v>
+        <v>3.620799999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-73.2978</v>
+        <v>-125.2731</v>
       </c>
       <c r="J19" t="n">
-        <v>155.9052</v>
+        <v>200.305</v>
       </c>
       <c r="K19" t="n">
-        <v>104.2013</v>
+        <v>145.4509</v>
       </c>
       <c r="L19" t="n">
-        <v>51.70579999999999</v>
+        <v>54.8536</v>
       </c>
       <c r="M19" t="n">
-        <v>-238.4458</v>
+        <v>-321.9612</v>
       </c>
       <c r="N19" t="n">
-        <v>-113.4447</v>
+        <v>-141.832</v>
       </c>
       <c r="O19" t="n">
-        <v>-125.0017</v>
+        <v>-180.1283</v>
       </c>
       <c r="P19" t="n">
-        <v>-56.7092</v>
+        <v>-64.8755</v>
       </c>
       <c r="Q19" t="n">
-        <v>-438.9229</v>
+        <v>-530.3836000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>382.2147</v>
+        <v>465.5095999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>0.07570000000000987</v>
+        <v>-3.137300000000004</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.8486</v>
+        <v>-16.5887</v>
       </c>
       <c r="U19" t="n">
-        <v>13.9231</v>
+        <v>13.4541</v>
       </c>
       <c r="V19" t="n">
-        <v>-17.1298</v>
+        <v>-35.7795</v>
       </c>
       <c r="W19" t="n">
-        <v>227.6014</v>
+        <v>259.2542</v>
       </c>
       <c r="X19" t="n">
-        <v>-244.7317</v>
+        <v>-295.0332999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Hiopos Lleida.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Hiopos Lleida.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>26.9946</v>
+        <v>26.0393</v>
       </c>
       <c r="E2" t="n">
-        <v>32.7956</v>
+        <v>33.3992</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.8009</v>
+        <v>-7.3599</v>
       </c>
       <c r="G2" t="n">
-        <v>11.1063</v>
+        <v>-15.4229</v>
       </c>
       <c r="H2" t="n">
-        <v>9.896800000000001</v>
+        <v>-6.831399999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2099</v>
+        <v>-8.591799999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>27.2633</v>
+        <v>21.0836</v>
       </c>
       <c r="K2" t="n">
-        <v>22.2307</v>
+        <v>9.2666</v>
       </c>
       <c r="L2" t="n">
-        <v>5.0323</v>
+        <v>11.8171</v>
       </c>
       <c r="M2" t="n">
-        <v>-16.1568</v>
+        <v>-36.5073</v>
       </c>
       <c r="N2" t="n">
-        <v>-12.3339</v>
+        <v>-16.0982</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.8224</v>
+        <v>-20.4088</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2274999999999996</v>
+        <v>-12.7476</v>
       </c>
       <c r="Q2" t="n">
-        <v>-27.7713</v>
+        <v>-68.2894</v>
       </c>
       <c r="R2" t="n">
-        <v>27.5437</v>
+        <v>55.5423</v>
       </c>
       <c r="S2" t="n">
-        <v>11.6484</v>
+        <v>-0.2007000000000002</v>
       </c>
       <c r="T2" t="n">
-        <v>8.201000000000001</v>
+        <v>-1.4656</v>
       </c>
       <c r="U2" t="n">
-        <v>3.4473</v>
+        <v>1.2651</v>
       </c>
       <c r="V2" t="n">
-        <v>4.4674</v>
+        <v>54.4106</v>
       </c>
       <c r="W2" t="n">
-        <v>25.1025</v>
+        <v>82.07089999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>-20.6352</v>
+        <v>-27.6601</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>11.8318</v>
+        <v>19.9582</v>
       </c>
       <c r="E3" t="n">
-        <v>4.837200000000001</v>
+        <v>27.1662</v>
       </c>
       <c r="F3" t="n">
-        <v>6.994800000000001</v>
+        <v>-7.208</v>
       </c>
       <c r="G3" t="n">
-        <v>-9.767299999999999</v>
+        <v>11.1063</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.8194</v>
+        <v>9.896800000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.9477</v>
+        <v>1.2099</v>
       </c>
       <c r="J3" t="n">
-        <v>17.5671</v>
+        <v>27.2633</v>
       </c>
       <c r="K3" t="n">
-        <v>7.7036</v>
+        <v>22.2307</v>
       </c>
       <c r="L3" t="n">
-        <v>9.863199999999999</v>
+        <v>5.0323</v>
       </c>
       <c r="M3" t="n">
-        <v>-27.3342</v>
+        <v>-16.1568</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.5234</v>
+        <v>-12.3339</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.811</v>
+        <v>-3.8224</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.186800000000001</v>
+        <v>-0.2274999999999996</v>
       </c>
       <c r="Q3" t="n">
-        <v>-59.1845</v>
+        <v>-27.7713</v>
       </c>
       <c r="R3" t="n">
-        <v>55.9976</v>
+        <v>27.5437</v>
       </c>
       <c r="S3" t="n">
-        <v>15.2051</v>
+        <v>4.6118</v>
       </c>
       <c r="T3" t="n">
-        <v>5.4114</v>
+        <v>2.5716</v>
       </c>
       <c r="U3" t="n">
-        <v>9.793900000000001</v>
+        <v>2.0403</v>
       </c>
       <c r="V3" t="n">
-        <v>9.580699999999998</v>
+        <v>4.4674</v>
       </c>
       <c r="W3" t="n">
-        <v>41.0427</v>
+        <v>25.1025</v>
       </c>
       <c r="X3" t="n">
-        <v>-31.462</v>
+        <v>-20.6352</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>10.33</v>
+        <v>8.273500000000002</v>
       </c>
       <c r="E4" t="n">
-        <v>39.0536</v>
+        <v>3.771599999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-28.7238</v>
+        <v>4.501799999999998</v>
       </c>
       <c r="G4" t="n">
-        <v>22.4576</v>
+        <v>-9.767299999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>23.6095</v>
+        <v>-7.8194</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1519</v>
+        <v>-1.9477</v>
       </c>
       <c r="J4" t="n">
-        <v>38.7481</v>
+        <v>17.5671</v>
       </c>
       <c r="K4" t="n">
-        <v>32.0829</v>
+        <v>7.7036</v>
       </c>
       <c r="L4" t="n">
-        <v>6.6651</v>
+        <v>9.863199999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>-16.2907</v>
+        <v>-27.3342</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.4735</v>
+        <v>-15.5234</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.8176</v>
+        <v>-11.811</v>
       </c>
       <c r="P4" t="n">
-        <v>-10.9264</v>
+        <v>-3.186800000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-39.1527</v>
+        <v>-59.1845</v>
       </c>
       <c r="R4" t="n">
-        <v>28.2268</v>
+        <v>55.9976</v>
       </c>
       <c r="S4" t="n">
-        <v>27.8126</v>
+        <v>11.6469</v>
       </c>
       <c r="T4" t="n">
-        <v>25.6378</v>
+        <v>4.346</v>
       </c>
       <c r="U4" t="n">
-        <v>2.175</v>
+        <v>7.301</v>
       </c>
       <c r="V4" t="n">
-        <v>-29.0136</v>
+        <v>9.580699999999998</v>
       </c>
       <c r="W4" t="n">
-        <v>13.8208</v>
+        <v>41.0427</v>
       </c>
       <c r="X4" t="n">
-        <v>-42.8348</v>
+        <v>-31.462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>O. PAULI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>5.718299999999997</v>
+        <v>4.2732</v>
       </c>
       <c r="E5" t="n">
-        <v>24.0415</v>
+        <v>4.121200000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-18.3235</v>
+        <v>0.151900000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-15.4229</v>
+        <v>5.675200000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-6.831399999999999</v>
+        <v>12.3437</v>
       </c>
       <c r="I5" t="n">
-        <v>-8.591799999999999</v>
+        <v>-6.6685</v>
       </c>
       <c r="J5" t="n">
-        <v>21.0836</v>
+        <v>45.3425</v>
       </c>
       <c r="K5" t="n">
-        <v>9.2666</v>
+        <v>31.1978</v>
       </c>
       <c r="L5" t="n">
-        <v>11.8171</v>
+        <v>14.1443</v>
       </c>
       <c r="M5" t="n">
-        <v>-36.5073</v>
+        <v>-39.6672</v>
       </c>
       <c r="N5" t="n">
-        <v>-16.0982</v>
+        <v>-18.8544</v>
       </c>
       <c r="O5" t="n">
-        <v>-20.4088</v>
+        <v>-20.8128</v>
       </c>
       <c r="P5" t="n">
-        <v>-12.7476</v>
+        <v>-11.6091</v>
       </c>
       <c r="Q5" t="n">
-        <v>-68.2894</v>
+        <v>-66.9237</v>
       </c>
       <c r="R5" t="n">
-        <v>55.5423</v>
+        <v>55.3148</v>
       </c>
       <c r="S5" t="n">
-        <v>-20.5217</v>
+        <v>-2.1998</v>
       </c>
       <c r="T5" t="n">
-        <v>-10.8234</v>
+        <v>-6.7256</v>
       </c>
       <c r="U5" t="n">
-        <v>-9.6981</v>
+        <v>4.5257</v>
       </c>
       <c r="V5" t="n">
-        <v>54.4106</v>
+        <v>12.4067</v>
       </c>
       <c r="W5" t="n">
-        <v>82.07089999999999</v>
+        <v>32.4283</v>
       </c>
       <c r="X5" t="n">
-        <v>-27.6601</v>
+        <v>-20.0213</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.697</v>
+        <v>-1.6657</v>
       </c>
       <c r="E6" t="n">
         <v>-1.3732</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3238</v>
+        <v>-0.2925</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4903</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2067</v>
+        <v>-0.1754</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0697</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.137</v>
+        <v>-0.1057</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. PAULI</t>
+          <t>I. DABO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.282299999999999</v>
+        <v>-4.662999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.0208</v>
+        <v>-0.6471</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7383</v>
+        <v>-4.0159</v>
       </c>
       <c r="G8" t="n">
-        <v>5.675200000000001</v>
+        <v>-0.6957</v>
       </c>
       <c r="H8" t="n">
-        <v>12.3437</v>
+        <v>-0.4337</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.6685</v>
+        <v>-0.2619</v>
       </c>
       <c r="J8" t="n">
-        <v>45.3425</v>
+        <v>0.9093</v>
       </c>
       <c r="K8" t="n">
-        <v>31.1978</v>
+        <v>0.3135</v>
       </c>
       <c r="L8" t="n">
-        <v>14.1443</v>
+        <v>0.5958</v>
       </c>
       <c r="M8" t="n">
-        <v>-39.6672</v>
+        <v>-1.605</v>
       </c>
       <c r="N8" t="n">
-        <v>-18.8544</v>
+        <v>-0.7472</v>
       </c>
       <c r="O8" t="n">
-        <v>-20.8128</v>
+        <v>-0.8577</v>
       </c>
       <c r="P8" t="n">
-        <v>-11.6091</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q8" t="n">
-        <v>-66.9237</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>55.3148</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-9.754999999999999</v>
+        <v>-0.6503</v>
       </c>
       <c r="T8" t="n">
-        <v>-15.8672</v>
+        <v>-0.4182</v>
       </c>
       <c r="U8" t="n">
-        <v>6.1124</v>
+        <v>-0.2321</v>
       </c>
       <c r="V8" t="n">
-        <v>12.4067</v>
+        <v>-2.1789</v>
       </c>
       <c r="W8" t="n">
-        <v>32.4283</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-20.0213</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. DABO</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6955</v>
+        <v>-7.144400000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6471</v>
+        <v>2.418699999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.0485</v>
+        <v>-9.5631</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6957</v>
+        <v>-4.305</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4337</v>
+        <v>12.7266</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2619</v>
+        <v>-17.0312</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9093</v>
+        <v>21.1299</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3135</v>
+        <v>21.1016</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5958</v>
+        <v>0.02820000000000034</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.605</v>
+        <v>-25.435</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7472</v>
+        <v>-8.375200000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8577</v>
+        <v>-17.0602</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1382</v>
+        <v>14.5684</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1382</v>
+        <v>-18.8934</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>33.4619</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6827</v>
+        <v>-2.5101</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4182</v>
+        <v>-1.711</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2645</v>
+        <v>-0.7991999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1789</v>
+        <v>-14.8977</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.8934</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1789</v>
+        <v>-16.791</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4288</v>
+        <v>-8.476599999999998</v>
       </c>
       <c r="E10" t="n">
-        <v>1.773099999999998</v>
+        <v>20.3953</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.201699999999999</v>
+        <v>-28.8719</v>
       </c>
       <c r="G10" t="n">
-        <v>-14.7188</v>
+        <v>22.4576</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.005299999999998</v>
+        <v>23.6095</v>
       </c>
       <c r="I10" t="n">
-        <v>-11.7135</v>
+        <v>-1.1519</v>
       </c>
       <c r="J10" t="n">
-        <v>13.5492</v>
+        <v>38.7481</v>
       </c>
       <c r="K10" t="n">
-        <v>1.894</v>
+        <v>32.0829</v>
       </c>
       <c r="L10" t="n">
-        <v>11.6549</v>
+        <v>6.6651</v>
       </c>
       <c r="M10" t="n">
-        <v>-28.2682</v>
+        <v>-16.2907</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.899500000000001</v>
+        <v>-8.4735</v>
       </c>
       <c r="O10" t="n">
-        <v>-23.3682</v>
+        <v>-7.8176</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2278000000000004</v>
+        <v>-10.9264</v>
       </c>
       <c r="Q10" t="n">
-        <v>-32.324</v>
+        <v>-39.1527</v>
       </c>
       <c r="R10" t="n">
-        <v>32.5519</v>
+        <v>28.2268</v>
       </c>
       <c r="S10" t="n">
-        <v>9.047499999999999</v>
+        <v>9.0061</v>
       </c>
       <c r="T10" t="n">
-        <v>7.831</v>
+        <v>6.9794</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2167</v>
+        <v>2.0272</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01510000000000006</v>
+        <v>-29.0136</v>
       </c>
       <c r="W10" t="n">
-        <v>12.7165</v>
+        <v>13.8208</v>
       </c>
       <c r="X10" t="n">
-        <v>-12.7013</v>
+        <v>-42.8348</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>-12.3123</v>
+        <v>-10.7141</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6137999999999986</v>
+        <v>-5.0895</v>
       </c>
       <c r="F11" t="n">
-        <v>-12.9259</v>
+        <v>-5.624699999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.305</v>
+        <v>-14.7188</v>
       </c>
       <c r="H11" t="n">
-        <v>12.7266</v>
+        <v>-3.005299999999998</v>
       </c>
       <c r="I11" t="n">
-        <v>-17.0312</v>
+        <v>-11.7135</v>
       </c>
       <c r="J11" t="n">
-        <v>21.1299</v>
+        <v>13.5492</v>
       </c>
       <c r="K11" t="n">
-        <v>21.1016</v>
+        <v>1.894</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02820000000000034</v>
+        <v>11.6549</v>
       </c>
       <c r="M11" t="n">
-        <v>-25.435</v>
+        <v>-28.2682</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.375200000000001</v>
+        <v>-4.899500000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-17.0602</v>
+        <v>-23.3682</v>
       </c>
       <c r="P11" t="n">
-        <v>14.5684</v>
+        <v>0.2278000000000004</v>
       </c>
       <c r="Q11" t="n">
-        <v>-18.8934</v>
+        <v>-32.324</v>
       </c>
       <c r="R11" t="n">
-        <v>33.4619</v>
+        <v>32.5519</v>
       </c>
       <c r="S11" t="n">
-        <v>-7.678</v>
+        <v>3.7623</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.5158</v>
+        <v>0.9686999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.162</v>
+        <v>2.7934</v>
       </c>
       <c r="V11" t="n">
-        <v>-14.8977</v>
+        <v>0.01510000000000006</v>
       </c>
       <c r="W11" t="n">
-        <v>1.8934</v>
+        <v>12.7165</v>
       </c>
       <c r="X11" t="n">
-        <v>-16.791</v>
+        <v>-12.7013</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>29</v>
       </c>
       <c r="D12" t="n">
-        <v>-15.4856</v>
+        <v>-10.8984</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6547</v>
+        <v>-1.0766</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.830500000000001</v>
+        <v>-9.821899999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-26.4352</v>
@@ -1390,13 +1390,13 @@
         <v>34.3726</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.116</v>
+        <v>0.4707</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.1432</v>
+        <v>-3.5655</v>
       </c>
       <c r="U12" t="n">
-        <v>4.0279</v>
+        <v>4.0366</v>
       </c>
       <c r="V12" t="n">
         <v>-6.1039</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ</t>
+          <t>D. GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.8092</v>
+        <v>-19.1153</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3896</v>
+        <v>-8.2254</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.4195</v>
+        <v>-10.8898</v>
       </c>
       <c r="G13" t="n">
-        <v>-11.0999</v>
+        <v>6.1402</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.7241</v>
+        <v>5.8229</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.3758</v>
+        <v>0.3171999999999992</v>
       </c>
       <c r="J13" t="n">
-        <v>3.025</v>
+        <v>19.6519</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1236999999999999</v>
+        <v>11.5771</v>
       </c>
       <c r="L13" t="n">
-        <v>3.1487</v>
+        <v>8.0749</v>
       </c>
       <c r="M13" t="n">
-        <v>-14.125</v>
+        <v>-13.5118</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.6006</v>
+        <v>-5.7542</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.5245</v>
+        <v>-7.7577</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8212</v>
+        <v>-11.6094</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.3331</v>
+        <v>-30.5026</v>
       </c>
       <c r="R13" t="n">
-        <v>7.5119</v>
+        <v>18.8933</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5622</v>
+        <v>0.3744</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9032</v>
+        <v>-1.9767</v>
       </c>
       <c r="U13" t="n">
-        <v>0.659</v>
+        <v>2.3511</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.4504</v>
+        <v>-14.0204</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0149999999999999</v>
+        <v>4.6021</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.4653</v>
+        <v>-18.6224</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. GARCIA</t>
+          <t>A. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>-24.2967</v>
+        <v>-19.1275</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.026</v>
+        <v>-6.7412</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.2706</v>
+        <v>-12.386</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1402</v>
+        <v>-11.0999</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8229</v>
+        <v>-7.7241</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3171999999999992</v>
+        <v>-3.3758</v>
       </c>
       <c r="J14" t="n">
-        <v>19.6519</v>
+        <v>3.025</v>
       </c>
       <c r="K14" t="n">
-        <v>11.5771</v>
+        <v>-0.1236999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>8.0749</v>
+        <v>3.1487</v>
       </c>
       <c r="M14" t="n">
-        <v>-13.5118</v>
+        <v>-14.125</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.7542</v>
+        <v>-7.6006</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.7577</v>
+        <v>-6.5245</v>
       </c>
       <c r="P14" t="n">
-        <v>-11.6094</v>
+        <v>-1.8212</v>
       </c>
       <c r="Q14" t="n">
-        <v>-30.5026</v>
+        <v>-9.3331</v>
       </c>
       <c r="R14" t="n">
-        <v>18.8933</v>
+        <v>7.5119</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.806999999999999</v>
+        <v>0.2439999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.777</v>
+        <v>-0.4485</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9703</v>
+        <v>0.6925999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-14.0204</v>
+        <v>-6.4504</v>
       </c>
       <c r="W14" t="n">
-        <v>4.6021</v>
+        <v>0.0149999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-18.6224</v>
+        <v>-6.4653</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>K. ZORIKS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>-27.5737</v>
+        <v>-20.1804</v>
       </c>
       <c r="E15" t="n">
-        <v>-29.7031</v>
+        <v>-13.9612</v>
       </c>
       <c r="F15" t="n">
-        <v>2.129300000000001</v>
+        <v>-6.219200000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-9.418799999999999</v>
+        <v>-7.035200000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>7.3565</v>
+        <v>-0.4663999999999998</v>
       </c>
       <c r="I15" t="n">
-        <v>-16.7755</v>
+        <v>-6.5692</v>
       </c>
       <c r="J15" t="n">
-        <v>4.870099999999999</v>
+        <v>-0.6634000000000005</v>
       </c>
       <c r="K15" t="n">
-        <v>12.0232</v>
+        <v>0.4732999999999998</v>
       </c>
       <c r="L15" t="n">
-        <v>-7.152800000000001</v>
+        <v>-1.1367</v>
       </c>
       <c r="M15" t="n">
-        <v>-14.2894</v>
+        <v>-6.371799999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.666700000000001</v>
+        <v>-0.9394000000000002</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.6227</v>
+        <v>-5.432</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.3818</v>
+        <v>-6.1462</v>
       </c>
       <c r="Q15" t="n">
-        <v>-38.9253</v>
+        <v>-17.9829</v>
       </c>
       <c r="R15" t="n">
-        <v>27.5436</v>
+        <v>11.8369</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3702</v>
+        <v>-3.6164</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3370000000000004</v>
+        <v>-1.0924</v>
       </c>
       <c r="U15" t="n">
-        <v>2.707</v>
+        <v>-2.5241</v>
       </c>
       <c r="V15" t="n">
-        <v>-9.1433</v>
+        <v>-3.3826</v>
       </c>
       <c r="W15" t="n">
-        <v>4.688499999999999</v>
+        <v>5.7779</v>
       </c>
       <c r="X15" t="n">
-        <v>-13.8317</v>
+        <v>-9.160500000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. ZORIKS</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D16" t="n">
-        <v>-27.5971</v>
+        <v>-27.3301</v>
       </c>
       <c r="E16" t="n">
-        <v>-19.18</v>
+        <v>-29.0271</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.417199999999999</v>
+        <v>1.6972</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.035200000000001</v>
+        <v>-9.418799999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4663999999999998</v>
+        <v>7.3565</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.5692</v>
+        <v>-16.7755</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6634000000000005</v>
+        <v>4.870099999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4732999999999998</v>
+        <v>12.0232</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.1367</v>
+        <v>-7.152800000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-6.371799999999999</v>
+        <v>-14.2894</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9394000000000002</v>
+        <v>-4.666700000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.432</v>
+        <v>-9.6227</v>
       </c>
       <c r="P16" t="n">
-        <v>-6.1462</v>
+        <v>-11.3818</v>
       </c>
       <c r="Q16" t="n">
-        <v>-17.9829</v>
+        <v>-38.9253</v>
       </c>
       <c r="R16" t="n">
-        <v>11.8369</v>
+        <v>27.5436</v>
       </c>
       <c r="S16" t="n">
-        <v>-11.0331</v>
+        <v>2.6135</v>
       </c>
       <c r="T16" t="n">
-        <v>-6.3111</v>
+        <v>0.3394</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.7217</v>
+        <v>2.2742</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.3826</v>
+        <v>-9.1433</v>
       </c>
       <c r="W16" t="n">
-        <v>5.7779</v>
+        <v>4.688499999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-9.160500000000001</v>
+        <v>-13.8317</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>-59.6153</v>
+        <v>-45.1343</v>
       </c>
       <c r="E17" t="n">
-        <v>-47.10429999999999</v>
+        <v>-35.7051</v>
       </c>
       <c r="F17" t="n">
-        <v>-12.5106</v>
+        <v>-9.4291</v>
       </c>
       <c r="G17" t="n">
         <v>-21.0415</v>
@@ -1780,13 +1780,13 @@
         <v>35.9661</v>
       </c>
       <c r="S17" t="n">
-        <v>-12.4931</v>
+        <v>1.9878</v>
       </c>
       <c r="T17" t="n">
-        <v>-12.9129</v>
+        <v>-1.5141</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4202000000000001</v>
+        <v>3.5016</v>
       </c>
       <c r="V17" t="n">
         <v>-17.2029</v>
@@ -1813,13 +1813,13 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>-78.40349999999999</v>
+        <v>-78.1938</v>
       </c>
       <c r="E18" t="n">
-        <v>-62.2215</v>
+        <v>-63.7815</v>
       </c>
       <c r="F18" t="n">
-        <v>-16.182</v>
+        <v>-14.4119</v>
       </c>
       <c r="G18" t="n">
         <v>-44.8432</v>
@@ -1858,13 +1858,13 @@
         <v>40.7462</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7376000000000001</v>
+        <v>0.9472999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6721000000000004</v>
+        <v>-0.8882000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.06560000000000021</v>
+        <v>1.8355</v>
       </c>
       <c r="V18" t="n">
         <v>-14.2663</v>
@@ -1891,19 +1891,19 @@
         <v>34</v>
       </c>
       <c r="D19" t="n">
-        <v>-225.4473</v>
+        <v>-196.2244</v>
       </c>
       <c r="E19" t="n">
-        <v>-87.41340000000002</v>
+        <v>-75.56360000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-138.0332</v>
+        <v>-120.6601</v>
       </c>
       <c r="G19" t="n">
         <v>-121.6537</v>
       </c>
       <c r="H19" t="n">
-        <v>3.620799999999999</v>
+        <v>3.620800000000003</v>
       </c>
       <c r="I19" t="n">
         <v>-125.2731</v>
@@ -1930,19 +1930,19 @@
         <v>-64.8755</v>
       </c>
       <c r="Q19" t="n">
-        <v>-530.3836000000001</v>
+        <v>-530.3836</v>
       </c>
       <c r="R19" t="n">
-        <v>465.5095999999999</v>
+        <v>465.5096</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.137300000000004</v>
+        <v>26.0845</v>
       </c>
       <c r="T19" t="n">
-        <v>-16.5887</v>
+        <v>-4.740100000000002</v>
       </c>
       <c r="U19" t="n">
-        <v>13.4541</v>
+        <v>30.8253</v>
       </c>
       <c r="V19" t="n">
         <v>-35.7795</v>
